--- a/backtest_runs/20260410_193731/by_symbol/SSML/SSML.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SSML/SSML.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>-10914.47999999999</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>89085.52000000002</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>89085.52000000002</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>93882.61000000002</v>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>93882.61000000002</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>93882.61000000002</v>
